--- a/08_project/List Update Hình SDA.xlsx
+++ b/08_project/List Update Hình SDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10705"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/loutruong/Documents/02_Financial well-being/14_Central Retail/01_code/08_project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://centralgroup-my.sharepoint.com/personal/thao_thimai_dang_vn_centralretail_com/Documents/WORKING FOLDER/1. HAND OVER/3. REPORT DAILY/01_code/loutruong/08_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9ECF667-88D0-1F4B-9591-B8F6EA0FD2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{D9ECF667-88D0-1F4B-9591-B8F6EA0FD2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B5848F9-D558-4838-B3BA-EAE9699927D3}"/>
   <bookViews>
-    <workbookView xWindow="-1580" yWindow="22360" windowWidth="41120" windowHeight="25820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="1" r:id="rId1"/>
@@ -14638,15 +14638,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F84"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>501</v>
       </c>
@@ -14663,7 +14663,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -14680,7 +14680,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>23</v>
       </c>
@@ -14695,7 +14695,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>34</v>
       </c>
@@ -14710,7 +14710,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>47</v>
       </c>
@@ -14725,7 +14725,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>63</v>
       </c>
@@ -14740,7 +14740,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>76</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>82</v>
       </c>
@@ -14770,7 +14770,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>90</v>
       </c>
@@ -14785,7 +14785,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>93</v>
       </c>
@@ -14800,7 +14800,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>96</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>99</v>
       </c>
@@ -14830,7 +14830,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>107</v>
       </c>
@@ -14845,7 +14845,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>117</v>
       </c>
@@ -14860,7 +14860,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>121</v>
       </c>
@@ -14875,7 +14875,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>124</v>
       </c>
@@ -14890,7 +14890,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>127</v>
       </c>
@@ -14905,7 +14905,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>136</v>
       </c>
@@ -14920,7 +14920,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>150</v>
       </c>
@@ -14935,7 +14935,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>160</v>
       </c>
@@ -14950,7 +14950,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>167</v>
       </c>
@@ -14965,7 +14965,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>176</v>
       </c>
@@ -14980,7 +14980,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>184</v>
       </c>
@@ -14995,7 +14995,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>193</v>
       </c>
@@ -15010,7 +15010,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>202</v>
       </c>
@@ -15025,7 +15025,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>210</v>
       </c>
@@ -15040,7 +15040,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>218</v>
       </c>
@@ -15055,7 +15055,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>226</v>
       </c>
@@ -15070,7 +15070,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>235</v>
       </c>
@@ -15085,7 +15085,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>244</v>
       </c>
@@ -15100,7 +15100,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>252</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>263</v>
       </c>
@@ -15130,7 +15130,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>273</v>
       </c>
@@ -15145,7 +15145,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>281</v>
       </c>
@@ -15160,7 +15160,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>290</v>
       </c>
@@ -15175,7 +15175,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>298</v>
       </c>
@@ -15190,7 +15190,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>308</v>
       </c>
@@ -15208,7 +15208,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>318</v>
       </c>
@@ -15223,7 +15223,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>329</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>339</v>
       </c>
@@ -15253,7 +15253,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>347</v>
       </c>
@@ -15268,7 +15268,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>355</v>
       </c>
@@ -15283,7 +15283,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>362</v>
       </c>
@@ -15298,7 +15298,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>369</v>
       </c>
@@ -15313,7 +15313,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>371</v>
       </c>
@@ -15328,7 +15328,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>373</v>
       </c>
@@ -15343,7 +15343,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>378</v>
       </c>
@@ -15358,7 +15358,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>383</v>
       </c>
@@ -15373,7 +15373,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>386</v>
       </c>
@@ -15388,7 +15388,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>393</v>
       </c>
@@ -15403,7 +15403,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>398</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>403</v>
       </c>
@@ -15433,7 +15433,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>410</v>
       </c>
@@ -15448,7 +15448,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>418</v>
       </c>
@@ -15463,7 +15463,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>428</v>
       </c>
@@ -15478,7 +15478,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>437</v>
       </c>
@@ -15493,7 +15493,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>444</v>
       </c>
@@ -15508,7 +15508,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>452</v>
       </c>
@@ -15523,7 +15523,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>459</v>
       </c>
@@ -15537,7 +15537,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>469</v>
       </c>
@@ -15551,7 +15551,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>474</v>
       </c>
@@ -15565,7 +15565,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
         <v>476</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
         <v>484</v>
       </c>
@@ -15593,7 +15593,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
         <v>493</v>
       </c>
@@ -15607,7 +15607,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="15" t="s">
         <v>614</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
         <v>616</v>
       </c>
@@ -15623,7 +15623,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
         <v>618</v>
       </c>
@@ -15631,7 +15631,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
         <v>620</v>
       </c>
@@ -15639,7 +15639,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
         <v>622</v>
       </c>
@@ -15647,7 +15647,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
         <v>624</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
         <v>626</v>
       </c>
@@ -15663,7 +15663,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
         <v>628</v>
       </c>
@@ -15671,7 +15671,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>630</v>
       </c>
@@ -15679,7 +15679,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
         <v>632</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
         <v>634</v>
       </c>
@@ -15695,7 +15695,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
         <v>636</v>
       </c>
@@ -15703,7 +15703,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
         <v>638</v>
       </c>
@@ -15711,7 +15711,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
         <v>640</v>
       </c>
@@ -15719,7 +15719,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
         <v>642</v>
       </c>
@@ -15727,7 +15727,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
         <v>644</v>
       </c>
@@ -15735,7 +15735,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
         <v>646</v>
       </c>
@@ -15743,7 +15743,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
         <v>648</v>
       </c>
@@ -15751,7 +15751,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="15"/>
     </row>
   </sheetData>
@@ -15830,14 +15830,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="16" customWidth="1"/>
-    <col min="2" max="3" width="150.83203125" style="16" customWidth="1"/>
-    <col min="4" max="16384" width="8.83203125" style="16"/>
+    <col min="2" max="3" width="150.85546875" style="16" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -15848,7 +15848,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="256" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="240" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>5</v>
       </c>
@@ -15859,7 +15859,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="405" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>23</v>
       </c>
@@ -15870,7 +15870,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>34</v>
       </c>
@@ -15881,7 +15881,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>47</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>63</v>
       </c>
@@ -15903,7 +15903,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="208" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="195" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>76</v>
       </c>
@@ -15914,7 +15914,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="176" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>82</v>
       </c>
@@ -15925,7 +15925,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="272" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="255" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>90</v>
       </c>
@@ -15936,7 +15936,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="272" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="255" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>93</v>
       </c>
@@ -15947,7 +15947,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="144" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>96</v>
       </c>
@@ -15958,7 +15958,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>99</v>
       </c>
@@ -15969,7 +15969,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>107</v>
       </c>
@@ -15980,7 +15980,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="144" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="150" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>117</v>
       </c>
@@ -15991,7 +15991,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="176" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="165" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>121</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="208" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="195" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>124</v>
       </c>
@@ -16013,7 +16013,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>127</v>
       </c>
@@ -16024,7 +16024,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="208" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="195" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>136</v>
       </c>
@@ -16035,7 +16035,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>150</v>
       </c>
@@ -16046,7 +16046,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>160</v>
       </c>
@@ -16057,7 +16057,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>167</v>
       </c>
@@ -16068,7 +16068,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>176</v>
       </c>
@@ -16079,7 +16079,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>184</v>
       </c>
@@ -16090,7 +16090,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>193</v>
       </c>
@@ -16101,7 +16101,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>202</v>
       </c>
@@ -16112,7 +16112,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>210</v>
       </c>
@@ -16123,7 +16123,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>218</v>
       </c>
@@ -16134,7 +16134,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>226</v>
       </c>
@@ -16145,7 +16145,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>235</v>
       </c>
@@ -16156,7 +16156,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>244</v>
       </c>
@@ -16167,7 +16167,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>252</v>
       </c>
@@ -16178,7 +16178,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>263</v>
       </c>
@@ -16189,7 +16189,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>273</v>
       </c>
@@ -16200,7 +16200,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>281</v>
       </c>
@@ -16211,7 +16211,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>290</v>
       </c>
@@ -16222,7 +16222,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>298</v>
       </c>
@@ -16233,7 +16233,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>308</v>
       </c>
@@ -16244,7 +16244,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>318</v>
       </c>
@@ -16255,7 +16255,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
         <v>329</v>
       </c>
@@ -16266,7 +16266,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
         <v>339</v>
       </c>
@@ -16277,7 +16277,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
         <v>347</v>
       </c>
@@ -16288,7 +16288,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
         <v>355</v>
       </c>
@@ -16299,7 +16299,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="365" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="345" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
         <v>362</v>
       </c>
@@ -16310,7 +16310,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
         <v>369</v>
       </c>
@@ -16318,7 +16318,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
         <v>371</v>
       </c>
@@ -16326,7 +16326,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
         <v>373</v>
       </c>
@@ -16337,7 +16337,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
         <v>378</v>
       </c>
@@ -16348,7 +16348,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
         <v>383</v>
       </c>
@@ -16359,7 +16359,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
         <v>386</v>
       </c>
@@ -16370,7 +16370,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
         <v>393</v>
       </c>
@@ -16381,7 +16381,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="365" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="390" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
         <v>398</v>
       </c>
@@ -16392,7 +16392,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
         <v>403</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
         <v>410</v>
       </c>
@@ -16414,7 +16414,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
         <v>418</v>
       </c>
@@ -16425,7 +16425,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
         <v>428</v>
       </c>
@@ -16436,7 +16436,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="395" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ht="390" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
         <v>437</v>
       </c>
@@ -16447,7 +16447,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="320" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="300" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
         <v>444</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="320" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ht="315" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
         <v>452</v>
       </c>
@@ -16469,7 +16469,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
         <v>459</v>
       </c>
@@ -16480,7 +16480,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
         <v>469</v>
       </c>
@@ -16491,7 +16491,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
         <v>474</v>
       </c>
@@ -16499,7 +16499,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
         <v>476</v>
       </c>
@@ -16510,7 +16510,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
         <v>484</v>
       </c>
@@ -16521,7 +16521,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
         <v>493</v>
       </c>
@@ -16532,92 +16532,92 @@
         <v>714</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="16" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="16" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
         <v>648</v>
       </c>
@@ -16632,9 +16632,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E374"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
@@ -16643,7 +16642,7 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16660,7 +16659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -16677,7 +16676,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -16694,7 +16693,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -16711,7 +16710,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -16728,7 +16727,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -16745,7 +16744,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -16762,7 +16761,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -16779,7 +16778,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -16796,7 +16795,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -16813,7 +16812,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -16830,7 +16829,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -16847,7 +16846,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -16864,7 +16863,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -16881,7 +16880,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -16898,7 +16897,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -16915,7 +16914,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -16932,7 +16931,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -16949,7 +16948,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -16966,7 +16965,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -16983,7 +16982,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -17000,7 +16999,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -17017,7 +17016,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -17034,7 +17033,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -17051,7 +17050,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -17068,7 +17067,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -17085,7 +17084,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -17102,7 +17101,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -17119,7 +17118,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -17136,7 +17135,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -17153,7 +17152,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -17170,7 +17169,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -17187,7 +17186,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -17204,7 +17203,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -17221,7 +17220,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -17238,7 +17237,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -17255,7 +17254,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -17272,7 +17271,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>47</v>
       </c>
@@ -17289,7 +17288,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -17306,7 +17305,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -17323,7 +17322,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -17340,7 +17339,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -17357,7 +17356,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -17374,7 +17373,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -17391,7 +17390,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -17408,7 +17407,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -17425,7 +17424,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -17442,7 +17441,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -17459,7 +17458,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -17476,7 +17475,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>47</v>
       </c>
@@ -17493,7 +17492,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>47</v>
       </c>
@@ -17510,7 +17509,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -17527,7 +17526,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>63</v>
       </c>
@@ -17544,7 +17543,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -17561,7 +17560,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -17578,7 +17577,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -17595,7 +17594,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -17612,7 +17611,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -17629,7 +17628,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -17646,7 +17645,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -17663,7 +17662,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -17680,7 +17679,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -17697,7 +17696,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>76</v>
       </c>
@@ -17714,7 +17713,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>76</v>
       </c>
@@ -17731,7 +17730,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>76</v>
       </c>
@@ -17748,7 +17747,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>76</v>
       </c>
@@ -17765,7 +17764,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>82</v>
       </c>
@@ -17782,7 +17781,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>82</v>
       </c>
@@ -17799,7 +17798,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>82</v>
       </c>
@@ -17816,7 +17815,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>82</v>
       </c>
@@ -17833,7 +17832,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>82</v>
       </c>
@@ -17850,7 +17849,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>82</v>
       </c>
@@ -17867,7 +17866,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>90</v>
       </c>
@@ -17884,7 +17883,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>93</v>
       </c>
@@ -17901,7 +17900,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>96</v>
       </c>
@@ -17918,7 +17917,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>99</v>
       </c>
@@ -17935,7 +17934,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>99</v>
       </c>
@@ -17952,7 +17951,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>99</v>
       </c>
@@ -17969,7 +17968,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>99</v>
       </c>
@@ -17986,7 +17985,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>99</v>
       </c>
@@ -18003,7 +18002,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>99</v>
       </c>
@@ -18020,7 +18019,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>107</v>
       </c>
@@ -18037,7 +18036,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -18054,7 +18053,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>107</v>
       </c>
@@ -18071,7 +18070,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>107</v>
       </c>
@@ -18088,7 +18087,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>107</v>
       </c>
@@ -18105,7 +18104,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>107</v>
       </c>
@@ -18122,7 +18121,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>107</v>
       </c>
@@ -18139,7 +18138,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>107</v>
       </c>
@@ -18156,7 +18155,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>117</v>
       </c>
@@ -18173,7 +18172,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>117</v>
       </c>
@@ -18190,7 +18189,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>121</v>
       </c>
@@ -18207,7 +18206,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>124</v>
       </c>
@@ -18224,7 +18223,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>127</v>
       </c>
@@ -18241,7 +18240,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>127</v>
       </c>
@@ -18258,7 +18257,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>127</v>
       </c>
@@ -18275,7 +18274,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>127</v>
       </c>
@@ -18292,7 +18291,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>127</v>
       </c>
@@ -18309,7 +18308,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -18326,7 +18325,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>127</v>
       </c>
@@ -18343,7 +18342,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>136</v>
       </c>
@@ -18360,7 +18359,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>136</v>
       </c>
@@ -18377,7 +18376,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>136</v>
       </c>
@@ -18394,7 +18393,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>136</v>
       </c>
@@ -18411,7 +18410,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>136</v>
       </c>
@@ -18428,7 +18427,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>136</v>
       </c>
@@ -18445,7 +18444,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>136</v>
       </c>
@@ -18462,7 +18461,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>136</v>
       </c>
@@ -18479,7 +18478,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>136</v>
       </c>
@@ -18496,7 +18495,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>136</v>
       </c>
@@ -18513,7 +18512,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>136</v>
       </c>
@@ -18530,7 +18529,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>136</v>
       </c>
@@ -18547,7 +18546,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>150</v>
       </c>
@@ -18564,7 +18563,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>150</v>
       </c>
@@ -18581,7 +18580,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>150</v>
       </c>
@@ -18598,7 +18597,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
@@ -18615,7 +18614,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>150</v>
       </c>
@@ -18632,7 +18631,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>150</v>
       </c>
@@ -18649,7 +18648,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>150</v>
       </c>
@@ -18666,7 +18665,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>150</v>
       </c>
@@ -18683,7 +18682,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>160</v>
       </c>
@@ -18700,7 +18699,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>160</v>
       </c>
@@ -18717,7 +18716,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>160</v>
       </c>
@@ -18734,7 +18733,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>160</v>
       </c>
@@ -18751,7 +18750,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>160</v>
       </c>
@@ -18768,7 +18767,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>167</v>
       </c>
@@ -18785,7 +18784,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>167</v>
       </c>
@@ -18802,7 +18801,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>167</v>
       </c>
@@ -18819,7 +18818,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>167</v>
       </c>
@@ -18836,7 +18835,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>167</v>
       </c>
@@ -18853,7 +18852,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>167</v>
       </c>
@@ -18870,7 +18869,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>167</v>
       </c>
@@ -18887,7 +18886,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>176</v>
       </c>
@@ -18904,7 +18903,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>176</v>
       </c>
@@ -18921,7 +18920,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>176</v>
       </c>
@@ -18938,7 +18937,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>176</v>
       </c>
@@ -18955,7 +18954,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>176</v>
       </c>
@@ -18972,7 +18971,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>176</v>
       </c>
@@ -18989,7 +18988,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>184</v>
       </c>
@@ -19006,7 +19005,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>184</v>
       </c>
@@ -19023,7 +19022,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>184</v>
       </c>
@@ -19040,7 +19039,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>184</v>
       </c>
@@ -19057,7 +19056,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>184</v>
       </c>
@@ -19074,7 +19073,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>184</v>
       </c>
@@ -19091,7 +19090,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>184</v>
       </c>
@@ -19108,7 +19107,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>193</v>
       </c>
@@ -19125,7 +19124,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>193</v>
       </c>
@@ -19142,7 +19141,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>193</v>
       </c>
@@ -19159,7 +19158,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>193</v>
       </c>
@@ -19176,7 +19175,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>193</v>
       </c>
@@ -19193,7 +19192,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>193</v>
       </c>
@@ -19210,7 +19209,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>193</v>
       </c>
@@ -19227,7 +19226,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>202</v>
       </c>
@@ -19244,7 +19243,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>202</v>
       </c>
@@ -19261,7 +19260,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>202</v>
       </c>
@@ -19278,7 +19277,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>202</v>
       </c>
@@ -19295,7 +19294,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>202</v>
       </c>
@@ -19312,7 +19311,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>202</v>
       </c>
@@ -19329,7 +19328,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>210</v>
       </c>
@@ -19346,7 +19345,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>210</v>
       </c>
@@ -19363,7 +19362,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>210</v>
       </c>
@@ -19380,7 +19379,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>210</v>
       </c>
@@ -19397,7 +19396,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>210</v>
       </c>
@@ -19414,7 +19413,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>210</v>
       </c>
@@ -19431,7 +19430,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>218</v>
       </c>
@@ -19448,7 +19447,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>218</v>
       </c>
@@ -19465,7 +19464,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>218</v>
       </c>
@@ -19482,7 +19481,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>218</v>
       </c>
@@ -19499,7 +19498,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>218</v>
       </c>
@@ -19516,7 +19515,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>218</v>
       </c>
@@ -19533,7 +19532,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>226</v>
       </c>
@@ -19550,7 +19549,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>226</v>
       </c>
@@ -19567,7 +19566,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>226</v>
       </c>
@@ -19584,7 +19583,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>226</v>
       </c>
@@ -19601,7 +19600,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>226</v>
       </c>
@@ -19618,7 +19617,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>226</v>
       </c>
@@ -19635,7 +19634,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>226</v>
       </c>
@@ -19652,7 +19651,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>235</v>
       </c>
@@ -19669,7 +19668,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>235</v>
       </c>
@@ -19686,7 +19685,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>235</v>
       </c>
@@ -19703,7 +19702,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>235</v>
       </c>
@@ -19720,7 +19719,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>235</v>
       </c>
@@ -19737,7 +19736,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>235</v>
       </c>
@@ -19754,7 +19753,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>235</v>
       </c>
@@ -19771,7 +19770,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>244</v>
       </c>
@@ -19788,7 +19787,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>244</v>
       </c>
@@ -19805,7 +19804,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>244</v>
       </c>
@@ -19822,7 +19821,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>244</v>
       </c>
@@ -19839,7 +19838,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>244</v>
       </c>
@@ -19856,7 +19855,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>244</v>
       </c>
@@ -19873,7 +19872,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>252</v>
       </c>
@@ -19890,7 +19889,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>252</v>
       </c>
@@ -19907,7 +19906,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>252</v>
       </c>
@@ -19924,7 +19923,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>252</v>
       </c>
@@ -19941,7 +19940,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>252</v>
       </c>
@@ -19958,7 +19957,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>252</v>
       </c>
@@ -19975,7 +19974,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>252</v>
       </c>
@@ -19992,7 +19991,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>252</v>
       </c>
@@ -20009,7 +20008,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>252</v>
       </c>
@@ -20026,7 +20025,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>263</v>
       </c>
@@ -20043,7 +20042,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>263</v>
       </c>
@@ -20060,7 +20059,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>263</v>
       </c>
@@ -20077,7 +20076,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>263</v>
       </c>
@@ -20094,7 +20093,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>263</v>
       </c>
@@ -20111,7 +20110,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>263</v>
       </c>
@@ -20128,7 +20127,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>263</v>
       </c>
@@ -20145,7 +20144,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>263</v>
       </c>
@@ -20162,7 +20161,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>273</v>
       </c>
@@ -20179,7 +20178,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>273</v>
       </c>
@@ -20196,7 +20195,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>273</v>
       </c>
@@ -20213,7 +20212,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>273</v>
       </c>
@@ -20230,7 +20229,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>273</v>
       </c>
@@ -20247,7 +20246,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>273</v>
       </c>
@@ -20264,7 +20263,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>281</v>
       </c>
@@ -20281,7 +20280,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>281</v>
       </c>
@@ -20298,7 +20297,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>281</v>
       </c>
@@ -20315,7 +20314,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>281</v>
       </c>
@@ -20332,7 +20331,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>281</v>
       </c>
@@ -20349,7 +20348,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>281</v>
       </c>
@@ -20366,7 +20365,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>281</v>
       </c>
@@ -20383,7 +20382,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>290</v>
       </c>
@@ -20400,7 +20399,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>290</v>
       </c>
@@ -20417,7 +20416,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>290</v>
       </c>
@@ -20434,7 +20433,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>290</v>
       </c>
@@ -20451,7 +20450,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>290</v>
       </c>
@@ -20468,7 +20467,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>290</v>
       </c>
@@ -20485,7 +20484,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>298</v>
       </c>
@@ -20502,7 +20501,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>298</v>
       </c>
@@ -20519,7 +20518,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>298</v>
       </c>
@@ -20536,7 +20535,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>298</v>
       </c>
@@ -20553,7 +20552,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>298</v>
       </c>
@@ -20570,7 +20569,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>298</v>
       </c>
@@ -20587,7 +20586,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>298</v>
       </c>
@@ -20604,7 +20603,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>298</v>
       </c>
@@ -20621,7 +20620,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>308</v>
       </c>
@@ -20638,7 +20637,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>308</v>
       </c>
@@ -20655,7 +20654,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>308</v>
       </c>
@@ -20672,7 +20671,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>308</v>
       </c>
@@ -20689,7 +20688,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>308</v>
       </c>
@@ -20706,7 +20705,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>308</v>
       </c>
@@ -20723,7 +20722,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>308</v>
       </c>
@@ -20740,7 +20739,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>308</v>
       </c>
@@ -20757,7 +20756,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>318</v>
       </c>
@@ -20774,7 +20773,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>318</v>
       </c>
@@ -20791,7 +20790,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>318</v>
       </c>
@@ -20808,7 +20807,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>318</v>
       </c>
@@ -20825,7 +20824,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>318</v>
       </c>
@@ -20842,7 +20841,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>318</v>
       </c>
@@ -20859,7 +20858,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>318</v>
       </c>
@@ -20876,7 +20875,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>318</v>
       </c>
@@ -20893,7 +20892,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>318</v>
       </c>
@@ -20910,7 +20909,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>329</v>
       </c>
@@ -20927,7 +20926,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>329</v>
       </c>
@@ -20944,7 +20943,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>329</v>
       </c>
@@ -20961,7 +20960,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>329</v>
       </c>
@@ -20978,7 +20977,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>329</v>
       </c>
@@ -20995,7 +20994,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>329</v>
       </c>
@@ -21012,7 +21011,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>329</v>
       </c>
@@ -21029,7 +21028,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>329</v>
       </c>
@@ -21046,7 +21045,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>339</v>
       </c>
@@ -21063,7 +21062,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>339</v>
       </c>
@@ -21080,7 +21079,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>339</v>
       </c>
@@ -21097,7 +21096,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>339</v>
       </c>
@@ -21114,7 +21113,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>339</v>
       </c>
@@ -21131,7 +21130,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>339</v>
       </c>
@@ -21148,7 +21147,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>347</v>
       </c>
@@ -21165,7 +21164,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>347</v>
       </c>
@@ -21182,7 +21181,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>347</v>
       </c>
@@ -21199,7 +21198,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>347</v>
       </c>
@@ -21216,7 +21215,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>347</v>
       </c>
@@ -21233,7 +21232,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>347</v>
       </c>
@@ -21250,7 +21249,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>355</v>
       </c>
@@ -21267,7 +21266,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>355</v>
       </c>
@@ -21284,7 +21283,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>355</v>
       </c>
@@ -21301,7 +21300,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>355</v>
       </c>
@@ -21318,7 +21317,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>355</v>
       </c>
@@ -21335,7 +21334,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>362</v>
       </c>
@@ -21352,7 +21351,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>362</v>
       </c>
@@ -21369,7 +21368,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>362</v>
       </c>
@@ -21386,7 +21385,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>362</v>
       </c>
@@ -21403,7 +21402,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>362</v>
       </c>
@@ -21420,7 +21419,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>369</v>
       </c>
@@ -21431,7 +21430,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>371</v>
       </c>
@@ -21442,7 +21441,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>373</v>
       </c>
@@ -21459,7 +21458,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>373</v>
       </c>
@@ -21476,7 +21475,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>373</v>
       </c>
@@ -21493,7 +21492,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>378</v>
       </c>
@@ -21510,7 +21509,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>378</v>
       </c>
@@ -21527,7 +21526,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>378</v>
       </c>
@@ -21544,7 +21543,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>383</v>
       </c>
@@ -21561,7 +21560,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>386</v>
       </c>
@@ -21578,7 +21577,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>386</v>
       </c>
@@ -21595,7 +21594,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>386</v>
       </c>
@@ -21612,7 +21611,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>386</v>
       </c>
@@ -21629,7 +21628,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>386</v>
       </c>
@@ -21646,7 +21645,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>393</v>
       </c>
@@ -21663,7 +21662,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>393</v>
       </c>
@@ -21680,7 +21679,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>393</v>
       </c>
@@ -21697,7 +21696,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>398</v>
       </c>
@@ -21714,7 +21713,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>398</v>
       </c>
@@ -21731,7 +21730,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>398</v>
       </c>
@@ -21748,7 +21747,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>403</v>
       </c>
@@ -21765,7 +21764,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>403</v>
       </c>
@@ -21782,7 +21781,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>403</v>
       </c>
@@ -21799,7 +21798,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>403</v>
       </c>
@@ -21816,7 +21815,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>403</v>
       </c>
@@ -21833,7 +21832,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>410</v>
       </c>
@@ -21850,7 +21849,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>410</v>
       </c>
@@ -21867,7 +21866,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>410</v>
       </c>
@@ -21884,7 +21883,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>410</v>
       </c>
@@ -21901,7 +21900,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>410</v>
       </c>
@@ -21918,7 +21917,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>410</v>
       </c>
@@ -21935,7 +21934,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>418</v>
       </c>
@@ -21952,7 +21951,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>418</v>
       </c>
@@ -21969,7 +21968,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>418</v>
       </c>
@@ -21986,7 +21985,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>418</v>
       </c>
@@ -22003,7 +22002,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>418</v>
       </c>
@@ -22020,7 +22019,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>418</v>
       </c>
@@ -22037,7 +22036,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>418</v>
       </c>
@@ -22054,7 +22053,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>418</v>
       </c>
@@ -22071,7 +22070,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>428</v>
       </c>
@@ -22088,7 +22087,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>428</v>
       </c>
@@ -22105,7 +22104,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>428</v>
       </c>
@@ -22122,7 +22121,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>428</v>
       </c>
@@ -22139,7 +22138,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>428</v>
       </c>
@@ -22156,7 +22155,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>428</v>
       </c>
@@ -22173,7 +22172,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>428</v>
       </c>
@@ -22190,7 +22189,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>437</v>
       </c>
@@ -22207,7 +22206,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>437</v>
       </c>
@@ -22224,7 +22223,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>437</v>
       </c>
@@ -22241,7 +22240,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>437</v>
       </c>
@@ -22258,7 +22257,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>437</v>
       </c>
@@ -22275,7 +22274,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>444</v>
       </c>
@@ -22292,7 +22291,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>444</v>
       </c>
@@ -22309,7 +22308,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>444</v>
       </c>
@@ -22326,7 +22325,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>444</v>
       </c>
@@ -22343,7 +22342,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>444</v>
       </c>
@@ -22360,7 +22359,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>444</v>
       </c>
@@ -22377,7 +22376,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>452</v>
       </c>
@@ -22394,7 +22393,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>452</v>
       </c>
@@ -22411,7 +22410,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>452</v>
       </c>
@@ -22428,7 +22427,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>452</v>
       </c>
@@ -22445,7 +22444,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>452</v>
       </c>
@@ -22462,7 +22461,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>459</v>
       </c>
@@ -22479,7 +22478,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>459</v>
       </c>
@@ -22496,7 +22495,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>459</v>
       </c>
@@ -22513,7 +22512,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>459</v>
       </c>
@@ -22530,7 +22529,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>459</v>
       </c>
@@ -22547,7 +22546,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>459</v>
       </c>
@@ -22564,7 +22563,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>459</v>
       </c>
@@ -22581,7 +22580,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>459</v>
       </c>
@@ -22598,7 +22597,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>469</v>
       </c>
@@ -22615,7 +22614,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>469</v>
       </c>
@@ -22632,7 +22631,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>469</v>
       </c>
@@ -22649,7 +22648,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>474</v>
       </c>
@@ -22666,7 +22665,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>476</v>
       </c>
@@ -22683,7 +22682,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>476</v>
       </c>
@@ -22700,7 +22699,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>476</v>
       </c>
@@ -22717,7 +22716,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>476</v>
       </c>
@@ -22734,7 +22733,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>476</v>
       </c>
@@ -22751,7 +22750,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>476</v>
       </c>
@@ -22768,7 +22767,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>484</v>
       </c>
@@ -22785,7 +22784,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>484</v>
       </c>
@@ -22802,7 +22801,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>484</v>
       </c>
@@ -22819,7 +22818,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>484</v>
       </c>
@@ -22836,7 +22835,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>484</v>
       </c>
@@ -22853,7 +22852,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>484</v>
       </c>
@@ -22870,7 +22869,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>484</v>
       </c>
@@ -22887,7 +22886,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>493</v>
       </c>
@@ -22904,7 +22903,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>493</v>
       </c>
@@ -22921,7 +22920,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>493</v>
       </c>
@@ -22938,7 +22937,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>493</v>
       </c>
@@ -22955,7 +22954,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>493</v>
       </c>
@@ -22972,7 +22971,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>493</v>
       </c>
@@ -22990,13 +22989,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E374" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="In-Active"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <hyperlinks>
     <hyperlink ref="D15" r:id="rId1" xr:uid="{02EF7253-B91C-1B44-9E19-D5B5A703A616}"/>
   </hyperlinks>
